--- a/erp-t-prescription/build/1.0.0/all-profiles.xlsx
+++ b/erp-t-prescription/build/1.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T07:08:59+00:00</t>
+    <t>2026-02-26T13:49:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/erp-t-prescription/build/1.0.0/all-profiles.xlsx
+++ b/erp-t-prescription/build/1.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T13:49:45+00:00</t>
+    <t>2026-02-26T16:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/erp-t-prescription/build/1.0.0/all-profiles.xlsx
+++ b/erp-t-prescription/build/1.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:08:04+00:00</t>
+    <t>2026-03-02T12:13:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/erp-t-prescription/build/1.0.0/all-profiles.xlsx
+++ b/erp-t-prescription/build/1.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T12:13:40+00:00</t>
+    <t>2026-03-03T06:38:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/erp-t-prescription/build/1.0.0/all-profiles.xlsx
+++ b/erp-t-prescription/build/1.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T06:38:17+00:00</t>
+    <t>2026-03-09T13:10:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
